--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96665</v>
+        <v>96668</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96668</v>
+        <v>96669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96669</v>
+        <v>96674</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -5093,7 +5093,7 @@
         <v>136858131</v>
       </c>
       <c r="B45" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>137032964</v>
       </c>
       <c r="B46" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>137033782</v>
       </c>
       <c r="B47" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>137033761</v>
       </c>
       <c r="B50" t="n">
-        <v>92831</v>
+        <v>92833</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>136858117</v>
       </c>
       <c r="B79" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>137033011</v>
       </c>
       <c r="B80" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>137033666</v>
       </c>
       <c r="B81" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>137033696</v>
       </c>
       <c r="B82" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>137033823</v>
       </c>
       <c r="B83" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>136858105</v>
       </c>
       <c r="B89" t="n">
-        <v>92126</v>
+        <v>92128</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>136858126</v>
       </c>
       <c r="B94" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>136858130</v>
       </c>
       <c r="B95" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>136858134</v>
       </c>
       <c r="B99" t="n">
-        <v>92948</v>
+        <v>92950</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>137033816</v>
       </c>
       <c r="B120" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>136858113</v>
       </c>
       <c r="B243" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>137033711</v>
       </c>
       <c r="B244" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>136858115</v>
       </c>
       <c r="B338" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ352"/>
+  <dimension ref="A1:AZ356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25828,45 +25828,45 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>135861275</v>
+        <v>137077842</v>
       </c>
       <c r="B245" t="n">
-        <v>80593</v>
+        <v>80597</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Lövbrännan, Ång</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>588922</v>
+        <v>589198</v>
       </c>
       <c r="R245" t="n">
-        <v>7042643</v>
+        <v>7042828</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25893,12 +25893,22 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -25913,65 +25923,65 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135861275</t>
+          <t>https://artportalen.se/Sighting/137077842</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>135862592</v>
+        <v>137078302</v>
       </c>
       <c r="B246" t="n">
-        <v>80593</v>
+        <v>80597</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>588849</v>
+        <v>589184</v>
       </c>
       <c r="R246" t="n">
-        <v>7042655</v>
+        <v>7042898</v>
       </c>
       <c r="S246" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -25995,12 +26005,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26015,27 +26025,27 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135862592</t>
+          <t>https://artportalen.se/Sighting/137078302</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127323663</v>
+        <v>135861275</v>
       </c>
       <c r="B247" t="n">
-        <v>80461</v>
+        <v>80593</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26043,21 +26053,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -26067,13 +26077,13 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>589112</v>
+        <v>588922</v>
       </c>
       <c r="R247" t="n">
-        <v>7042785</v>
+        <v>7042643</v>
       </c>
       <c r="S247" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -26097,12 +26107,12 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26117,24 +26127,24 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323663</t>
+          <t>https://artportalen.se/Sighting/135861275</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>135838386</v>
+        <v>135862592</v>
       </c>
       <c r="B248" t="n">
         <v>80593</v>
@@ -26145,34 +26155,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Lövbrännan, Lövbrännan, Ång</t>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>589173</v>
+        <v>588849</v>
       </c>
       <c r="R248" t="n">
-        <v>7042793</v>
+        <v>7042655</v>
       </c>
       <c r="S248" t="n">
         <v>15</v>
@@ -26199,12 +26209,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26230,16 +26240,16 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135838386</t>
+          <t>https://artportalen.se/Sighting/135862592</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>135838463</v>
+        <v>127323663</v>
       </c>
       <c r="B249" t="n">
-        <v>80593</v>
+        <v>80461</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26271,10 +26281,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>589142</v>
+        <v>589112</v>
       </c>
       <c r="R249" t="n">
-        <v>7042846</v>
+        <v>7042785</v>
       </c>
       <c r="S249" t="n">
         <v>15</v>
@@ -26301,12 +26311,12 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26332,13 +26342,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135838463</t>
+          <t>https://artportalen.se/Sighting/127323663</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>135840594</v>
+        <v>135838386</v>
       </c>
       <c r="B250" t="n">
         <v>80593</v>
@@ -26369,14 +26379,14 @@
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Lövbrännan, Lövbrännan, Ång</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>588983</v>
+        <v>589173</v>
       </c>
       <c r="R250" t="n">
-        <v>7042772</v>
+        <v>7042793</v>
       </c>
       <c r="S250" t="n">
         <v>15</v>
@@ -26434,13 +26444,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840594</t>
+          <t>https://artportalen.se/Sighting/135838386</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>135841605</v>
+        <v>135838463</v>
       </c>
       <c r="B251" t="n">
         <v>80593</v>
@@ -26475,10 +26485,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>588948</v>
+        <v>589142</v>
       </c>
       <c r="R251" t="n">
-        <v>7042799</v>
+        <v>7042846</v>
       </c>
       <c r="S251" t="n">
         <v>15</v>
@@ -26536,13 +26546,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135841605</t>
+          <t>https://artportalen.se/Sighting/135838463</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135842223</v>
+        <v>135840594</v>
       </c>
       <c r="B252" t="n">
         <v>80593</v>
@@ -26577,10 +26587,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>588864</v>
+        <v>588983</v>
       </c>
       <c r="R252" t="n">
-        <v>7042749</v>
+        <v>7042772</v>
       </c>
       <c r="S252" t="n">
         <v>15</v>
@@ -26638,13 +26648,13 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135842223</t>
+          <t>https://artportalen.se/Sighting/135840594</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135844937</v>
+        <v>135841605</v>
       </c>
       <c r="B253" t="n">
         <v>80593</v>
@@ -26679,10 +26689,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>588544</v>
+        <v>588948</v>
       </c>
       <c r="R253" t="n">
-        <v>7042720</v>
+        <v>7042799</v>
       </c>
       <c r="S253" t="n">
         <v>15</v>
@@ -26740,16 +26750,16 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135844937</t>
+          <t>https://artportalen.se/Sighting/135841605</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135863003</v>
+        <v>135842223</v>
       </c>
       <c r="B254" t="n">
-        <v>80594</v>
+        <v>80593</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26781,13 +26791,13 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>588915</v>
+        <v>588864</v>
       </c>
       <c r="R254" t="n">
-        <v>7042726</v>
+        <v>7042749</v>
       </c>
       <c r="S254" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -26811,12 +26821,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -26831,27 +26841,27 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135863003</t>
+          <t>https://artportalen.se/Sighting/135842223</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>135863725</v>
+        <v>135844937</v>
       </c>
       <c r="B255" t="n">
-        <v>80594</v>
+        <v>80593</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26883,10 +26893,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>588811</v>
+        <v>588544</v>
       </c>
       <c r="R255" t="n">
-        <v>7042723</v>
+        <v>7042720</v>
       </c>
       <c r="S255" t="n">
         <v>15</v>
@@ -26913,12 +26923,12 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -26944,16 +26954,16 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135863725</t>
+          <t>https://artportalen.se/Sighting/135844937</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127323603</v>
+        <v>135863003</v>
       </c>
       <c r="B256" t="n">
-        <v>80467</v>
+        <v>80594</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26961,21 +26971,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26985,13 +26995,13 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>589107</v>
+        <v>588915</v>
       </c>
       <c r="R256" t="n">
-        <v>7042787</v>
+        <v>7042726</v>
       </c>
       <c r="S256" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -27015,12 +27025,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27035,27 +27045,27 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323603</t>
+          <t>https://artportalen.se/Sighting/135863003</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>135838525</v>
+        <v>135863725</v>
       </c>
       <c r="B257" t="n">
-        <v>80599</v>
+        <v>80594</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27063,21 +27073,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -27087,10 +27097,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>589134</v>
+        <v>588811</v>
       </c>
       <c r="R257" t="n">
-        <v>7042853</v>
+        <v>7042723</v>
       </c>
       <c r="S257" t="n">
         <v>15</v>
@@ -27117,12 +27127,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27148,16 +27158,16 @@
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135838525</t>
+          <t>https://artportalen.se/Sighting/135863725</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>135840621</v>
+        <v>127323603</v>
       </c>
       <c r="B258" t="n">
-        <v>80599</v>
+        <v>80467</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27189,10 +27199,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>588983</v>
+        <v>589107</v>
       </c>
       <c r="R258" t="n">
-        <v>7042771</v>
+        <v>7042787</v>
       </c>
       <c r="S258" t="n">
         <v>15</v>
@@ -27219,12 +27229,12 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27250,13 +27260,13 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840621</t>
+          <t>https://artportalen.se/Sighting/127323603</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>135841511</v>
+        <v>135838525</v>
       </c>
       <c r="B259" t="n">
         <v>80599</v>
@@ -27291,10 +27301,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>588936</v>
+        <v>589134</v>
       </c>
       <c r="R259" t="n">
-        <v>7042765</v>
+        <v>7042853</v>
       </c>
       <c r="S259" t="n">
         <v>15</v>
@@ -27352,13 +27362,13 @@
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135841511</t>
+          <t>https://artportalen.se/Sighting/135838525</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>135844505</v>
+        <v>135840621</v>
       </c>
       <c r="B260" t="n">
         <v>80599</v>
@@ -27393,10 +27403,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>588579</v>
+        <v>588983</v>
       </c>
       <c r="R260" t="n">
-        <v>7042694</v>
+        <v>7042771</v>
       </c>
       <c r="S260" t="n">
         <v>15</v>
@@ -27454,16 +27464,16 @@
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135844505</t>
+          <t>https://artportalen.se/Sighting/135840621</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>135841344</v>
+        <v>135841511</v>
       </c>
       <c r="B261" t="n">
-        <v>80600</v>
+        <v>80599</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27471,21 +27481,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27495,10 +27505,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>588942</v>
+        <v>588936</v>
       </c>
       <c r="R261" t="n">
-        <v>7042787</v>
+        <v>7042765</v>
       </c>
       <c r="S261" t="n">
         <v>15</v>
@@ -27556,16 +27566,16 @@
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135841344</t>
+          <t>https://artportalen.se/Sighting/135841511</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>135841515</v>
+        <v>135844505</v>
       </c>
       <c r="B262" t="n">
-        <v>80600</v>
+        <v>80599</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -27573,21 +27583,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27597,10 +27607,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>588936</v>
+        <v>588579</v>
       </c>
       <c r="R262" t="n">
-        <v>7042765</v>
+        <v>7042694</v>
       </c>
       <c r="S262" t="n">
         <v>15</v>
@@ -27658,16 +27668,16 @@
       <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135841515</t>
+          <t>https://artportalen.se/Sighting/135844505</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>135859643</v>
+        <v>135841344</v>
       </c>
       <c r="B263" t="n">
-        <v>80601</v>
+        <v>80600</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -27699,13 +27709,13 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>589097</v>
+        <v>588942</v>
       </c>
       <c r="R263" t="n">
-        <v>7042712</v>
+        <v>7042787</v>
       </c>
       <c r="S263" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27729,12 +27739,12 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -27749,27 +27759,27 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135859643</t>
+          <t>https://artportalen.se/Sighting/135841344</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>135862930</v>
+        <v>135841515</v>
       </c>
       <c r="B264" t="n">
-        <v>80601</v>
+        <v>80600</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27801,13 +27811,13 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>588915</v>
+        <v>588936</v>
       </c>
       <c r="R264" t="n">
-        <v>7042732</v>
+        <v>7042765</v>
       </c>
       <c r="S264" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -27831,12 +27841,12 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -27851,24 +27861,24 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135862930</t>
+          <t>https://artportalen.se/Sighting/135841515</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>135864867</v>
+        <v>135859643</v>
       </c>
       <c r="B265" t="n">
         <v>80601</v>
@@ -27903,10 +27913,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>588691</v>
+        <v>589097</v>
       </c>
       <c r="R265" t="n">
-        <v>7042729</v>
+        <v>7042712</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27964,38 +27974,38 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864867</t>
+          <t>https://artportalen.se/Sighting/135859643</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>135862824</v>
+        <v>135862930</v>
       </c>
       <c r="B266" t="n">
-        <v>78478</v>
+        <v>80601</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -28005,13 +28015,13 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>588852</v>
+        <v>588915</v>
       </c>
       <c r="R266" t="n">
-        <v>7042633</v>
+        <v>7042732</v>
       </c>
       <c r="S266" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28055,27 +28065,27 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135862824</t>
+          <t>https://artportalen.se/Sighting/135862930</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>135839191</v>
+        <v>135864867</v>
       </c>
       <c r="B267" t="n">
-        <v>58003</v>
+        <v>80601</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -28083,42 +28093,37 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P267" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>589082</v>
+        <v>588691</v>
       </c>
       <c r="R267" t="n">
-        <v>7042810</v>
+        <v>7042729</v>
       </c>
       <c r="S267" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28142,17 +28147,12 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i grov asp</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28167,27 +28167,27 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135839191</t>
+          <t>https://artportalen.se/Sighting/135864867</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>135840320</v>
+        <v>135862824</v>
       </c>
       <c r="B268" t="n">
-        <v>58006</v>
+        <v>78478</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -28195,39 +28195,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P268" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>589008</v>
+        <v>588852</v>
       </c>
       <c r="R268" t="n">
-        <v>7042762</v>
+        <v>7042633</v>
       </c>
       <c r="S268" t="n">
         <v>15</v>
@@ -28254,17 +28249,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28290,33 +28280,33 @@
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840320</t>
+          <t>https://artportalen.se/Sighting/135862824</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>135841452</v>
+        <v>135839191</v>
       </c>
       <c r="B269" t="n">
-        <v>58006</v>
+        <v>58003</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -28327,7 +28317,7 @@
       <c r="I269" t="inlineStr"/>
       <c r="M269" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
@@ -28336,10 +28326,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>588939</v>
+        <v>589082</v>
       </c>
       <c r="R269" t="n">
-        <v>7042780</v>
+        <v>7042810</v>
       </c>
       <c r="S269" t="n">
         <v>15</v>
@@ -28376,7 +28366,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Gammalt bohål i grov asp</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28402,13 +28392,13 @@
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135841452</t>
+          <t>https://artportalen.se/Sighting/135839191</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>135845487</v>
+        <v>135840320</v>
       </c>
       <c r="B270" t="n">
         <v>58006</v>
@@ -28439,7 +28429,7 @@
       <c r="I270" t="inlineStr"/>
       <c r="M270" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
@@ -28448,10 +28438,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>588652</v>
+        <v>589008</v>
       </c>
       <c r="R270" t="n">
-        <v>7042753</v>
+        <v>7042762</v>
       </c>
       <c r="S270" t="n">
         <v>15</v>
@@ -28488,7 +28478,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>Gammalt bohål i asplåga, ca 4 cm diameter.</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28514,13 +28504,13 @@
       <c r="AY270" t="inlineStr"/>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135845487</t>
+          <t>https://artportalen.se/Sighting/135840320</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>135860019</v>
+        <v>135841452</v>
       </c>
       <c r="B271" t="n">
         <v>58006</v>
@@ -28549,19 +28539,24 @@
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>589028</v>
+        <v>588939</v>
       </c>
       <c r="R271" t="n">
-        <v>7042730</v>
+        <v>7042780</v>
       </c>
       <c r="S271" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -28585,27 +28580,17 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AC271" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -28620,24 +28605,24 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135860019</t>
+          <t>https://artportalen.se/Sighting/135841452</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>135861257</v>
+        <v>135845487</v>
       </c>
       <c r="B272" t="n">
         <v>58006</v>
@@ -28668,7 +28653,7 @@
       <c r="I272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
@@ -28677,13 +28662,13 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>588929</v>
+        <v>588652</v>
       </c>
       <c r="R272" t="n">
-        <v>7042664</v>
+        <v>7042753</v>
       </c>
       <c r="S272" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -28707,27 +28692,17 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Gammalt bohål i asplåga, ca 4 cm diameter.</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -28742,24 +28717,24 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135861257</t>
+          <t>https://artportalen.se/Sighting/135845487</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>135861815</v>
+        <v>135860019</v>
       </c>
       <c r="B273" t="n">
         <v>58006</v>
@@ -28788,21 +28763,16 @@
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>588887</v>
+        <v>589028</v>
       </c>
       <c r="R273" t="n">
-        <v>7042709</v>
+        <v>7042730</v>
       </c>
       <c r="S273" t="n">
         <v>20</v>
@@ -28834,7 +28804,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -28844,12 +28814,12 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -28875,13 +28845,13 @@
       <c r="AY273" t="inlineStr"/>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135861815</t>
+          <t>https://artportalen.se/Sighting/135860019</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>135862454</v>
+        <v>135861257</v>
       </c>
       <c r="B274" t="n">
         <v>58006</v>
@@ -28921,10 +28891,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>588856</v>
+        <v>588929</v>
       </c>
       <c r="R274" t="n">
-        <v>7042625</v>
+        <v>7042664</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28956,7 +28926,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -28966,7 +28936,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -28997,13 +28967,13 @@
       <c r="AY274" t="inlineStr"/>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135862454</t>
+          <t>https://artportalen.se/Sighting/135861257</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>135862813</v>
+        <v>135861815</v>
       </c>
       <c r="B275" t="n">
         <v>58006</v>
@@ -29043,13 +29013,13 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>588891</v>
+        <v>588887</v>
       </c>
       <c r="R275" t="n">
-        <v>7042706</v>
+        <v>7042709</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -29078,7 +29048,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -29088,7 +29058,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -29108,24 +29078,24 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135862813</t>
+          <t>https://artportalen.se/Sighting/135861815</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>135864221</v>
+        <v>135862454</v>
       </c>
       <c r="B276" t="n">
         <v>58006</v>
@@ -29153,14 +29123,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="I276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
@@ -29169,13 +29135,13 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>588719</v>
+        <v>588856</v>
       </c>
       <c r="R276" t="n">
-        <v>7042737</v>
+        <v>7042625</v>
       </c>
       <c r="S276" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -29202,9 +29168,24 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -29219,24 +29200,24 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864221</t>
+          <t>https://artportalen.se/Sighting/135862454</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>135864598</v>
+        <v>135862813</v>
       </c>
       <c r="B277" t="n">
         <v>58006</v>
@@ -29265,14 +29246,9 @@
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
@@ -29281,10 +29257,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>588769</v>
+        <v>588891</v>
       </c>
       <c r="R277" t="n">
-        <v>7042725</v>
+        <v>7042706</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -29316,7 +29292,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -29326,7 +29302,12 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -29352,13 +29333,13 @@
       <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864598</t>
+          <t>https://artportalen.se/Sighting/135862813</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>135870456</v>
+        <v>135864221</v>
       </c>
       <c r="B278" t="n">
         <v>58006</v>
@@ -29386,15 +29367,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
@@ -29403,13 +29383,13 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>588952</v>
+        <v>588719</v>
       </c>
       <c r="R278" t="n">
-        <v>7042830</v>
+        <v>7042737</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -29436,19 +29416,9 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>18:53</t>
-        </is>
-      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t>18:53</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -29463,62 +29433,72 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135870456</t>
+          <t>https://artportalen.se/Sighting/135864221</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>135867126</v>
+        <v>135864598</v>
       </c>
       <c r="B279" t="n">
-        <v>4777</v>
+        <v>58006</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>588617</v>
+        <v>588769</v>
       </c>
       <c r="R279" t="n">
-        <v>7042666</v>
+        <v>7042725</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29548,14 +29528,19 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -29570,62 +29555,72 @@
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135867126</t>
+          <t>https://artportalen.se/Sighting/135864598</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>135870763</v>
+        <v>135870456</v>
       </c>
       <c r="B280" t="n">
-        <v>12377</v>
+        <v>58006</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>101283</v>
+        <v>100109</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P280" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>588846</v>
+        <v>588952</v>
       </c>
       <c r="R280" t="n">
-        <v>7042786</v>
+        <v>7042830</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29655,14 +29650,19 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AC280" t="inlineStr">
-        <is>
-          <t>Kläckhål och larvgång i björkhögstubbe med fnösktickor.</t>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -29677,65 +29677,65 @@
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135870763</t>
+          <t>https://artportalen.se/Sighting/135870456</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>135879820</v>
+        <v>135867126</v>
       </c>
       <c r="B281" t="n">
-        <v>12377</v>
+        <v>4777</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>101283</v>
+        <v>100299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>588833</v>
+        <v>588617</v>
       </c>
       <c r="R281" t="n">
-        <v>7042783</v>
+        <v>7042666</v>
       </c>
       <c r="S281" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>Kläckhål och larvgång i björkhögstubbe med fnösktickor</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -29795,55 +29795,51 @@
       <c r="AY281" t="inlineStr"/>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135879820</t>
+          <t>https://artportalen.se/Sighting/135867126</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>135866991</v>
+        <v>135870763</v>
       </c>
       <c r="B282" t="n">
-        <v>10983</v>
+        <v>12377</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>101449</v>
+        <v>101283</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Djupsvart brunbagge</t>
+        </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>588599</v>
+        <v>588846</v>
       </c>
       <c r="R282" t="n">
-        <v>7042687</v>
+        <v>7042786</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29878,6 +29874,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>Kläckhål och larvgång i björkhögstubbe med fnösktickor.</t>
+        </is>
+      </c>
       <c r="AD282" t="b">
         <v>0</v>
       </c>
@@ -29901,58 +29902,54 @@
       <c r="AY282" t="inlineStr"/>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135866991</t>
+          <t>https://artportalen.se/Sighting/135870763</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>135869197</v>
+        <v>135879820</v>
       </c>
       <c r="B283" t="n">
-        <v>10983</v>
+        <v>12377</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>101449</v>
+        <v>101283</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Djupsvart brunbagge</t>
+        </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>588771</v>
+        <v>588833</v>
       </c>
       <c r="R283" t="n">
-        <v>7042738</v>
+        <v>7042783</v>
       </c>
       <c r="S283" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -29982,6 +29979,11 @@
       <c r="AA283" t="inlineStr">
         <is>
           <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>Kläckhål och larvgång i björkhögstubbe med fnösktickor</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -30007,16 +30009,16 @@
       <c r="AY283" t="inlineStr"/>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135869197</t>
+          <t>https://artportalen.se/Sighting/135879820</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>135860214</v>
+        <v>135866991</v>
       </c>
       <c r="B284" t="n">
-        <v>6289</v>
+        <v>10983</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30024,34 +30026,38 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>101520</v>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Större flatbagge</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Peltis grossa</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr"/>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P284" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>588997</v>
+        <v>588599</v>
       </c>
       <c r="R284" t="n">
-        <v>7042693</v>
+        <v>7042687</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -30086,11 +30092,6 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AC284" t="inlineStr">
-        <is>
-          <t>Flera kläckhål</t>
-        </is>
-      </c>
       <c r="AD284" t="b">
         <v>0</v>
       </c>
@@ -30114,64 +30115,55 @@
       <c r="AY284" t="inlineStr"/>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135860214</t>
+          <t>https://artportalen.se/Sighting/135866991</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>135865377</v>
+        <v>135869197</v>
       </c>
       <c r="B285" t="n">
-        <v>18844</v>
+        <v>10983</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>101797</v>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>Karelsk barkfluga</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Xylomya czekanovskii</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Pleske, 1925</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P285" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>588698</v>
+        <v>588771</v>
       </c>
       <c r="R285" t="n">
-        <v>7042744</v>
+        <v>7042738</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -30206,18 +30198,12 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AC285" t="inlineStr">
-        <is>
-          <t>9 puppor</t>
-        </is>
-      </c>
       <c r="AD285" t="b">
         <v>0</v>
       </c>
       <c r="AE285" t="b">
         <v>0</v>
       </c>
-      <c r="AF285" t="inlineStr"/>
       <c r="AG285" t="b">
         <v>0</v>
       </c>
@@ -30229,65 +30215,60 @@
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Kim Hultgren, Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135865377</t>
+          <t>https://artportalen.se/Sighting/135869197</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>135870053</v>
+        <v>135860214</v>
       </c>
       <c r="B286" t="n">
-        <v>18844</v>
+        <v>6289</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>101797</v>
+        <v>101520</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Karelsk barkfluga</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Xylomya czekanovskii</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Pleske, 1925</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>588822</v>
+        <v>588997</v>
       </c>
       <c r="R286" t="n">
-        <v>7042830</v>
+        <v>7042693</v>
       </c>
       <c r="S286" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -30321,7 +30302,7 @@
       </c>
       <c r="AC286" t="inlineStr">
         <is>
-          <t>3 puppor</t>
+          <t>Flera kläckhål</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -30336,24 +30317,24 @@
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135870053</t>
+          <t>https://artportalen.se/Sighting/135860214</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>135879817</v>
+        <v>135865377</v>
       </c>
       <c r="B287" t="n">
         <v>18844</v>
@@ -30383,7 +30364,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J287" t="inlineStr"/>
@@ -30397,17 +30378,17 @@
       <c r="N287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>588814</v>
+        <v>588698</v>
       </c>
       <c r="R287" t="n">
-        <v>7042809</v>
+        <v>7042744</v>
       </c>
       <c r="S287" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -30441,7 +30422,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>3 puppor</t>
+          <t>9 puppor</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -30462,19 +30443,19 @@
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, Kim Hultgren</t>
+          <t>Erland Lindblad, Kim Hultgren, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135879817</t>
+          <t>https://artportalen.se/Sighting/135865377</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>136858103</v>
+        <v>135870053</v>
       </c>
       <c r="B288" t="n">
         <v>18844</v>
@@ -30502,11 +30483,7 @@
           <t>Pleske, 1925</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
           <t>larv/nymf</t>
@@ -30514,17 +30491,17 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Lövbränna vid Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>588641</v>
+        <v>588822</v>
       </c>
       <c r="R288" t="n">
-        <v>7042682</v>
+        <v>7042830</v>
       </c>
       <c r="S288" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -30548,12 +30525,17 @@
       </c>
       <c r="Y288" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>3 puppor</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -30568,28 +30550,24 @@
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Kristin Lindström, Anna-Maria Eriksson, Pernilla Hansson</t>
-        </is>
-      </c>
-      <c r="AY288" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr"/>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136858103</t>
+          <t>https://artportalen.se/Sighting/135870053</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>136858107</v>
+        <v>135879817</v>
       </c>
       <c r="B289" t="n">
         <v>18844</v>
@@ -30619,27 +30597,31 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
           <t>puppa</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Lövbränna vid Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>588949</v>
+        <v>588814</v>
       </c>
       <c r="R289" t="n">
-        <v>7042768</v>
+        <v>7042809</v>
       </c>
       <c r="S289" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -30663,12 +30645,17 @@
       </c>
       <c r="Y289" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>3 puppor</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -30677,80 +30664,81 @@
       <c r="AE289" t="b">
         <v>0</v>
       </c>
+      <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="b">
         <v>0</v>
       </c>
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Kristin Lindström, Anna-Maria Eriksson, Pernilla Hansson</t>
-        </is>
-      </c>
-      <c r="AY289" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman, Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr"/>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136858107</t>
+          <t>https://artportalen.se/Sighting/135879817</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>135844397</v>
+        <v>136858103</v>
       </c>
       <c r="B290" t="n">
-        <v>58167</v>
+        <v>18844</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>103021</v>
+        <v>101797</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Karelsk barkfluga</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Xylomya czekanovskii</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr"/>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>Pleske, 1925</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Lövbränna vid Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>588595</v>
+        <v>588641</v>
       </c>
       <c r="R290" t="n">
-        <v>7042676</v>
+        <v>7042682</v>
       </c>
       <c r="S290" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -30774,12 +30762,12 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -30794,76 +30782,75 @@
       <c r="AT290" t="inlineStr"/>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kristin Lindström</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY290" t="inlineStr"/>
+          <t>Kristin Lindström, Anna-Maria Eriksson, Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135844397</t>
+          <t>https://artportalen.se/Sighting/136858103</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>135859797</v>
+        <v>136858107</v>
       </c>
       <c r="B291" t="n">
-        <v>58167</v>
+        <v>18844</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>103021</v>
+        <v>101797</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Karelsk barkfluga</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Xylomya czekanovskii</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pleske, 1925</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>puppa</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Lövbränna vid Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>589048</v>
+        <v>588949</v>
       </c>
       <c r="R291" t="n">
-        <v>7042734</v>
+        <v>7042768</v>
       </c>
       <c r="S291" t="n">
         <v>20</v>
@@ -30890,22 +30877,12 @@
       </c>
       <c r="Y291" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="Z291" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -30920,65 +30897,74 @@
       <c r="AT291" t="inlineStr"/>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kristin Lindström</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY291" t="inlineStr"/>
+          <t>Kristin Lindström, Anna-Maria Eriksson, Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
       <c r="AZ291" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135859797</t>
+          <t>https://artportalen.se/Sighting/136858107</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>135863220</v>
+        <v>135844397</v>
       </c>
       <c r="B292" t="n">
-        <v>8452</v>
+        <v>58167</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P292" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>588911</v>
+        <v>588595</v>
       </c>
       <c r="R292" t="n">
-        <v>7042752</v>
+        <v>7042676</v>
       </c>
       <c r="S292" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -31002,17 +30988,12 @@
       </c>
       <c r="Y292" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AC292" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -31027,27 +31008,27 @@
       <c r="AT292" t="inlineStr"/>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
       <c r="AZ292" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135863220</t>
+          <t>https://artportalen.se/Sighting/135844397</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>135844584</v>
+        <v>135859797</v>
       </c>
       <c r="B293" t="n">
-        <v>56570</v>
+        <v>58167</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31055,27 +31036,36 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -31084,13 +31074,13 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>588590</v>
+        <v>589048</v>
       </c>
       <c r="R293" t="n">
-        <v>7042674</v>
+        <v>7042734</v>
       </c>
       <c r="S293" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -31114,12 +31104,22 @@
       </c>
       <c r="Y293" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -31134,27 +31134,27 @@
       <c r="AT293" t="inlineStr"/>
       <c r="AW293" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
       <c r="AZ293" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135844584</t>
+          <t>https://artportalen.se/Sighting/135859797</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>135856895</v>
+        <v>135863220</v>
       </c>
       <c r="B294" t="n">
-        <v>98363</v>
+        <v>8452</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31162,21 +31162,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>219815</v>
+        <v>106554</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -31186,13 +31186,13 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>589185</v>
+        <v>588911</v>
       </c>
       <c r="R294" t="n">
-        <v>7042761</v>
+        <v>7042752</v>
       </c>
       <c r="S294" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -31222,6 +31222,11 @@
       <c r="AA294" t="inlineStr">
         <is>
           <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AC294" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -31236,62 +31241,67 @@
       <c r="AT294" t="inlineStr"/>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135856895</t>
+          <t>https://artportalen.se/Sighting/135863220</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>135856870</v>
+        <v>135844584</v>
       </c>
       <c r="B295" t="n">
-        <v>108367</v>
+        <v>56570</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>220083</v>
+        <v>206004</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P295" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>589190</v>
+        <v>588590</v>
       </c>
       <c r="R295" t="n">
-        <v>7042769</v>
+        <v>7042674</v>
       </c>
       <c r="S295" t="n">
         <v>15</v>
@@ -31318,12 +31328,12 @@
       </c>
       <c r="Y295" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -31349,16 +31359,16 @@
       <c r="AY295" t="inlineStr"/>
       <c r="AZ295" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135856870</t>
+          <t>https://artportalen.se/Sighting/135844584</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>135857313</v>
+        <v>135856895</v>
       </c>
       <c r="B296" t="n">
-        <v>111317</v>
+        <v>98363</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31366,21 +31376,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>220240</v>
+        <v>219815</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -31390,13 +31400,13 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>589131</v>
+        <v>589185</v>
       </c>
       <c r="R296" t="n">
-        <v>7042778</v>
+        <v>7042761</v>
       </c>
       <c r="S296" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -31440,66 +31450,62 @@
       <c r="AT296" t="inlineStr"/>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
       <c r="AZ296" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135857313</t>
+          <t>https://artportalen.se/Sighting/135856895</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>127323690</v>
+        <v>135856870</v>
       </c>
       <c r="B297" t="n">
-        <v>99118</v>
+        <v>108367</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>589123</v>
+        <v>589190</v>
       </c>
       <c r="R297" t="n">
-        <v>7042802</v>
+        <v>7042769</v>
       </c>
       <c r="S297" t="n">
         <v>15</v>
@@ -31526,12 +31532,12 @@
       </c>
       <c r="Y297" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -31557,58 +31563,54 @@
       <c r="AY297" t="inlineStr"/>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323690</t>
+          <t>https://artportalen.se/Sighting/135856870</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>127323749</v>
+        <v>137078308</v>
       </c>
       <c r="B298" t="n">
-        <v>99118</v>
+        <v>108386</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>589080</v>
+        <v>589183</v>
       </c>
       <c r="R298" t="n">
-        <v>7042746</v>
+        <v>7042891</v>
       </c>
       <c r="S298" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -31632,12 +31634,12 @@
       </c>
       <c r="Y298" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -31652,74 +31654,65 @@
       <c r="AT298" t="inlineStr"/>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127323749</t>
+          <t>https://artportalen.se/Sighting/137078308</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>135839938</v>
+        <v>135857313</v>
       </c>
       <c r="B299" t="n">
-        <v>99341</v>
+        <v>111317</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>589056</v>
+        <v>589131</v>
       </c>
       <c r="R299" t="n">
-        <v>7042806</v>
+        <v>7042778</v>
       </c>
       <c r="S299" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
@@ -31743,12 +31736,12 @@
       </c>
       <c r="Y299" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -31763,27 +31756,27 @@
       <c r="AT299" t="inlineStr"/>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135839938</t>
+          <t>https://artportalen.se/Sighting/135857313</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>135841204</v>
+        <v>127323690</v>
       </c>
       <c r="B300" t="n">
-        <v>99341</v>
+        <v>99118</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31810,12 +31803,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
@@ -31824,10 +31812,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>588958</v>
+        <v>589123</v>
       </c>
       <c r="R300" t="n">
-        <v>7042788</v>
+        <v>7042802</v>
       </c>
       <c r="S300" t="n">
         <v>15</v>
@@ -31854,12 +31842,12 @@
       </c>
       <c r="Y300" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -31885,16 +31873,16 @@
       <c r="AY300" t="inlineStr"/>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135841204</t>
+          <t>https://artportalen.se/Sighting/127323690</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>135841251</v>
+        <v>127323749</v>
       </c>
       <c r="B301" t="n">
-        <v>99341</v>
+        <v>99118</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -31921,12 +31909,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
@@ -31935,10 +31918,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>588961</v>
+        <v>589080</v>
       </c>
       <c r="R301" t="n">
-        <v>7042791</v>
+        <v>7042746</v>
       </c>
       <c r="S301" t="n">
         <v>15</v>
@@ -31965,12 +31948,12 @@
       </c>
       <c r="Y301" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -31996,13 +31979,13 @@
       <c r="AY301" t="inlineStr"/>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135841251</t>
+          <t>https://artportalen.se/Sighting/127323749</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>135844085</v>
+        <v>135839938</v>
       </c>
       <c r="B302" t="n">
         <v>99341</v>
@@ -32032,7 +32015,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -32046,10 +32029,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>588640</v>
+        <v>589056</v>
       </c>
       <c r="R302" t="n">
-        <v>7042686</v>
+        <v>7042806</v>
       </c>
       <c r="S302" t="n">
         <v>15</v>
@@ -32107,13 +32090,13 @@
       <c r="AY302" t="inlineStr"/>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135844085</t>
+          <t>https://artportalen.se/Sighting/135839938</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>135844774</v>
+        <v>135841204</v>
       </c>
       <c r="B303" t="n">
         <v>99341</v>
@@ -32143,7 +32126,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
@@ -32152,10 +32140,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>588560</v>
+        <v>588958</v>
       </c>
       <c r="R303" t="n">
-        <v>7042724</v>
+        <v>7042788</v>
       </c>
       <c r="S303" t="n">
         <v>15</v>
@@ -32213,13 +32201,13 @@
       <c r="AY303" t="inlineStr"/>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135844774</t>
+          <t>https://artportalen.se/Sighting/135841204</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>135845274</v>
+        <v>135841251</v>
       </c>
       <c r="B304" t="n">
         <v>99341</v>
@@ -32249,7 +32237,7 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -32263,10 +32251,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>588544</v>
+        <v>588961</v>
       </c>
       <c r="R304" t="n">
-        <v>7042738</v>
+        <v>7042791</v>
       </c>
       <c r="S304" t="n">
         <v>15</v>
@@ -32324,13 +32312,13 @@
       <c r="AY304" t="inlineStr"/>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135845274</t>
+          <t>https://artportalen.se/Sighting/135841251</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>135845458</v>
+        <v>135844085</v>
       </c>
       <c r="B305" t="n">
         <v>99341</v>
@@ -32360,7 +32348,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P305" t="inlineStr">
@@ -32369,10 +32362,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>588642</v>
+        <v>588640</v>
       </c>
       <c r="R305" t="n">
-        <v>7042761</v>
+        <v>7042686</v>
       </c>
       <c r="S305" t="n">
         <v>15</v>
@@ -32430,16 +32423,16 @@
       <c r="AY305" t="inlineStr"/>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135845458</t>
+          <t>https://artportalen.se/Sighting/135844085</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>135857308</v>
+        <v>135844774</v>
       </c>
       <c r="B306" t="n">
-        <v>99342</v>
+        <v>99341</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32466,7 +32459,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
@@ -32475,10 +32468,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>589137</v>
+        <v>588560</v>
       </c>
       <c r="R306" t="n">
-        <v>7042777</v>
+        <v>7042724</v>
       </c>
       <c r="S306" t="n">
         <v>15</v>
@@ -32505,12 +32498,12 @@
       </c>
       <c r="Y306" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -32536,16 +32529,16 @@
       <c r="AY306" t="inlineStr"/>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135857308</t>
+          <t>https://artportalen.se/Sighting/135844774</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>135858017</v>
+        <v>135845274</v>
       </c>
       <c r="B307" t="n">
-        <v>99342</v>
+        <v>99341</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32572,7 +32565,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P307" t="inlineStr">
@@ -32581,10 +32579,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>589135</v>
+        <v>588544</v>
       </c>
       <c r="R307" t="n">
-        <v>7042800</v>
+        <v>7042738</v>
       </c>
       <c r="S307" t="n">
         <v>15</v>
@@ -32611,12 +32609,12 @@
       </c>
       <c r="Y307" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -32642,16 +32640,16 @@
       <c r="AY307" t="inlineStr"/>
       <c r="AZ307" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135858017</t>
+          <t>https://artportalen.se/Sighting/135845274</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>135858106</v>
+        <v>135845458</v>
       </c>
       <c r="B308" t="n">
-        <v>99342</v>
+        <v>99341</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -32676,20 +32674,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr"/>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P308" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>589127</v>
+        <v>588642</v>
       </c>
       <c r="R308" t="n">
-        <v>7042817</v>
+        <v>7042761</v>
       </c>
       <c r="S308" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -32713,12 +32715,12 @@
       </c>
       <c r="Y308" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -32733,24 +32735,24 @@
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135858106</t>
+          <t>https://artportalen.se/Sighting/135845458</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>135858631</v>
+        <v>135857308</v>
       </c>
       <c r="B309" t="n">
         <v>99342</v>
@@ -32780,7 +32782,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
@@ -32789,10 +32791,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>589115</v>
+        <v>589137</v>
       </c>
       <c r="R309" t="n">
-        <v>7042860</v>
+        <v>7042777</v>
       </c>
       <c r="S309" t="n">
         <v>15</v>
@@ -32850,13 +32852,13 @@
       <c r="AY309" t="inlineStr"/>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135858631</t>
+          <t>https://artportalen.se/Sighting/135857308</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>135859788</v>
+        <v>135858017</v>
       </c>
       <c r="B310" t="n">
         <v>99342</v>
@@ -32886,12 +32888,7 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
@@ -32900,10 +32897,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>589059</v>
+        <v>589135</v>
       </c>
       <c r="R310" t="n">
-        <v>7042712</v>
+        <v>7042800</v>
       </c>
       <c r="S310" t="n">
         <v>15</v>
@@ -32961,13 +32958,13 @@
       <c r="AY310" t="inlineStr"/>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135859788</t>
+          <t>https://artportalen.se/Sighting/135858017</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>135860011</v>
+        <v>135858106</v>
       </c>
       <c r="B311" t="n">
         <v>99342</v>
@@ -32995,21 +32992,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>589034</v>
+        <v>589127</v>
       </c>
       <c r="R311" t="n">
-        <v>7042729</v>
+        <v>7042817</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -33039,19 +33032,9 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA311" t="inlineStr">
         <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB311" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -33066,24 +33049,24 @@
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135860011</t>
+          <t>https://artportalen.se/Sighting/135858106</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>135860130</v>
+        <v>135858631</v>
       </c>
       <c r="B312" t="n">
         <v>99342</v>
@@ -33113,12 +33096,7 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P312" t="inlineStr">
@@ -33127,10 +33105,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>589049</v>
+        <v>589115</v>
       </c>
       <c r="R312" t="n">
-        <v>7042709</v>
+        <v>7042860</v>
       </c>
       <c r="S312" t="n">
         <v>15</v>
@@ -33188,13 +33166,13 @@
       <c r="AY312" t="inlineStr"/>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135860130</t>
+          <t>https://artportalen.se/Sighting/135858631</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>135860668</v>
+        <v>135859788</v>
       </c>
       <c r="B313" t="n">
         <v>99342</v>
@@ -33224,7 +33202,7 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -33238,10 +33216,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>588914</v>
+        <v>589059</v>
       </c>
       <c r="R313" t="n">
-        <v>7042731</v>
+        <v>7042712</v>
       </c>
       <c r="S313" t="n">
         <v>15</v>
@@ -33299,13 +33277,13 @@
       <c r="AY313" t="inlineStr"/>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135860668</t>
+          <t>https://artportalen.se/Sighting/135859788</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>135863056</v>
+        <v>135860011</v>
       </c>
       <c r="B314" t="n">
         <v>99342</v>
@@ -33333,17 +33311,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr"/>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P314" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>588881</v>
+        <v>589034</v>
       </c>
       <c r="R314" t="n">
-        <v>7042730</v>
+        <v>7042729</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -33373,9 +33355,19 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA314" t="inlineStr">
         <is>
           <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -33390,24 +33382,24 @@
       <c r="AT314" t="inlineStr"/>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135863056</t>
+          <t>https://artportalen.se/Sighting/135860011</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>135863790</v>
+        <v>135860130</v>
       </c>
       <c r="B315" t="n">
         <v>99342</v>
@@ -33437,7 +33429,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
@@ -33446,13 +33443,13 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>588793</v>
+        <v>589049</v>
       </c>
       <c r="R315" t="n">
-        <v>7042721</v>
+        <v>7042709</v>
       </c>
       <c r="S315" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
@@ -33479,19 +33476,9 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA315" t="inlineStr">
         <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB315" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -33506,24 +33493,24 @@
       <c r="AT315" t="inlineStr"/>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135863790</t>
+          <t>https://artportalen.se/Sighting/135860130</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>135864635</v>
+        <v>135860668</v>
       </c>
       <c r="B316" t="n">
         <v>99342</v>
@@ -33553,7 +33540,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P316" t="inlineStr">
@@ -33562,10 +33554,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>588702</v>
+        <v>588914</v>
       </c>
       <c r="R316" t="n">
-        <v>7042696</v>
+        <v>7042731</v>
       </c>
       <c r="S316" t="n">
         <v>15</v>
@@ -33623,13 +33615,13 @@
       <c r="AY316" t="inlineStr"/>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864635</t>
+          <t>https://artportalen.se/Sighting/135860668</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>135864833</v>
+        <v>135863056</v>
       </c>
       <c r="B317" t="n">
         <v>99342</v>
@@ -33657,24 +33649,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>588659</v>
+        <v>588881</v>
       </c>
       <c r="R317" t="n">
-        <v>7042719</v>
+        <v>7042730</v>
       </c>
       <c r="S317" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -33718,24 +33706,24 @@
       <c r="AT317" t="inlineStr"/>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864833</t>
+          <t>https://artportalen.se/Sighting/135863056</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>135866243</v>
+        <v>135863790</v>
       </c>
       <c r="B318" t="n">
         <v>99342</v>
@@ -33765,7 +33753,7 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P318" t="inlineStr">
@@ -33774,10 +33762,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>588588</v>
+        <v>588793</v>
       </c>
       <c r="R318" t="n">
-        <v>7042713</v>
+        <v>7042721</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -33809,7 +33797,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -33819,7 +33807,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -33845,13 +33833,13 @@
       <c r="AY318" t="inlineStr"/>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135866243</t>
+          <t>https://artportalen.se/Sighting/135863790</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>135867025</v>
+        <v>135864635</v>
       </c>
       <c r="B319" t="n">
         <v>99342</v>
@@ -33881,7 +33869,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P319" t="inlineStr">
@@ -33890,13 +33878,13 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>588565</v>
+        <v>588702</v>
       </c>
       <c r="R319" t="n">
-        <v>7042669</v>
+        <v>7042696</v>
       </c>
       <c r="S319" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -33923,19 +33911,9 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AA319" t="inlineStr">
         <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB319" t="inlineStr">
-        <is>
-          <t>16:51</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -33950,24 +33928,24 @@
       <c r="AT319" t="inlineStr"/>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
       <c r="AZ319" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135867025</t>
+          <t>https://artportalen.se/Sighting/135864635</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>135868685</v>
+        <v>135864833</v>
       </c>
       <c r="B320" t="n">
         <v>99342</v>
@@ -33997,12 +33975,7 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">
@@ -34011,10 +33984,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>588619</v>
+        <v>588659</v>
       </c>
       <c r="R320" t="n">
-        <v>7042663</v>
+        <v>7042719</v>
       </c>
       <c r="S320" t="n">
         <v>15</v>
@@ -34072,13 +34045,13 @@
       <c r="AY320" t="inlineStr"/>
       <c r="AZ320" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135868685</t>
+          <t>https://artportalen.se/Sighting/135864833</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>135869575</v>
+        <v>135866243</v>
       </c>
       <c r="B321" t="n">
         <v>99342</v>
@@ -34108,12 +34081,7 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P321" t="inlineStr">
@@ -34122,13 +34090,13 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>588785</v>
+        <v>588588</v>
       </c>
       <c r="R321" t="n">
-        <v>7042766</v>
+        <v>7042713</v>
       </c>
       <c r="S321" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -34155,9 +34123,19 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA321" t="inlineStr">
         <is>
           <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -34172,24 +34150,24 @@
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
       <c r="AZ321" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135869575</t>
+          <t>https://artportalen.se/Sighting/135866243</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>135870113</v>
+        <v>135867025</v>
       </c>
       <c r="B322" t="n">
         <v>99342</v>
@@ -34219,12 +34197,7 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P322" t="inlineStr">
@@ -34233,13 +34206,13 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>588800</v>
+        <v>588565</v>
       </c>
       <c r="R322" t="n">
-        <v>7042809</v>
+        <v>7042669</v>
       </c>
       <c r="S322" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -34266,9 +34239,19 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
       <c r="AA322" t="inlineStr">
         <is>
           <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -34283,24 +34266,24 @@
       <c r="AT322" t="inlineStr"/>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
       <c r="AZ322" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135870113</t>
+          <t>https://artportalen.se/Sighting/135867025</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>135870199</v>
+        <v>135868685</v>
       </c>
       <c r="B323" t="n">
         <v>99342</v>
@@ -34328,20 +34311,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P323" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>588792</v>
+        <v>588619</v>
       </c>
       <c r="R323" t="n">
-        <v>7042788</v>
+        <v>7042663</v>
       </c>
       <c r="S323" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -34385,24 +34377,24 @@
       <c r="AT323" t="inlineStr"/>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135870199</t>
+          <t>https://artportalen.se/Sighting/135868685</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>135870459</v>
+        <v>135869575</v>
       </c>
       <c r="B324" t="n">
         <v>99342</v>
@@ -34432,7 +34424,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
@@ -34441,10 +34438,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>588954</v>
+        <v>588785</v>
       </c>
       <c r="R324" t="n">
-        <v>7042836</v>
+        <v>7042766</v>
       </c>
       <c r="S324" t="n">
         <v>15</v>
@@ -34502,13 +34499,13 @@
       <c r="AY324" t="inlineStr"/>
       <c r="AZ324" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135870459</t>
+          <t>https://artportalen.se/Sighting/135869575</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>135879816</v>
+        <v>135870113</v>
       </c>
       <c r="B325" t="n">
         <v>99342</v>
@@ -34536,20 +34533,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>588790</v>
+        <v>588800</v>
       </c>
       <c r="R325" t="n">
-        <v>7042792</v>
+        <v>7042809</v>
       </c>
       <c r="S325" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -34593,49 +34599,49 @@
       <c r="AT325" t="inlineStr"/>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
       <c r="AZ325" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135879816</t>
+          <t>https://artportalen.se/Sighting/135870113</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>135840334</v>
+        <v>135870199</v>
       </c>
       <c r="B326" t="n">
-        <v>98203</v>
+        <v>99342</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
@@ -34645,13 +34651,13 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>589001</v>
+        <v>588792</v>
       </c>
       <c r="R326" t="n">
-        <v>7042763</v>
+        <v>7042788</v>
       </c>
       <c r="S326" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -34675,12 +34681,12 @@
       </c>
       <c r="Y326" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD326" t="b">
@@ -34695,65 +34701,69 @@
       <c r="AT326" t="inlineStr"/>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
       <c r="AZ326" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840334</t>
+          <t>https://artportalen.se/Sighting/135870199</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>135860341</v>
+        <v>135870459</v>
       </c>
       <c r="B327" t="n">
-        <v>98204</v>
+        <v>99342</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I327" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P327" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>588992</v>
+        <v>588954</v>
       </c>
       <c r="R327" t="n">
-        <v>7042690</v>
+        <v>7042836</v>
       </c>
       <c r="S327" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -34797,65 +34807,65 @@
       <c r="AT327" t="inlineStr"/>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
       <c r="AZ327" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135860341</t>
+          <t>https://artportalen.se/Sighting/135870459</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>135864246</v>
+        <v>135879816</v>
       </c>
       <c r="B328" t="n">
-        <v>99148</v>
+        <v>99342</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>223049</v>
+        <v>220787</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>588725</v>
+        <v>588790</v>
       </c>
       <c r="R328" t="n">
-        <v>7042729</v>
+        <v>7042792</v>
       </c>
       <c r="S328" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -34910,51 +34920,51 @@
       <c r="AY328" t="inlineStr"/>
       <c r="AZ328" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864246</t>
+          <t>https://artportalen.se/Sighting/135879816</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>135864056</v>
+        <v>137078295</v>
       </c>
       <c r="B329" t="n">
-        <v>98393</v>
+        <v>99361</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>588708</v>
+        <v>589190</v>
       </c>
       <c r="R329" t="n">
-        <v>7042743</v>
+        <v>7042907</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -34981,12 +34991,17 @@
       </c>
       <c r="Y329" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -35012,16 +35027,16 @@
       <c r="AY329" t="inlineStr"/>
       <c r="AZ329" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864056</t>
+          <t>https://artportalen.se/Sighting/137078295</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>135841306</v>
+        <v>135840334</v>
       </c>
       <c r="B330" t="n">
-        <v>80538</v>
+        <v>98203</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -35029,21 +35044,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -35053,10 +35068,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>588936</v>
+        <v>589001</v>
       </c>
       <c r="R330" t="n">
-        <v>7042791</v>
+        <v>7042763</v>
       </c>
       <c r="S330" t="n">
         <v>15</v>
@@ -35114,16 +35129,16 @@
       <c r="AY330" t="inlineStr"/>
       <c r="AZ330" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135841306</t>
+          <t>https://artportalen.se/Sighting/135840334</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>135841732</v>
+        <v>135860341</v>
       </c>
       <c r="B331" t="n">
-        <v>80538</v>
+        <v>98204</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -35131,21 +35146,21 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -35155,13 +35170,13 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>588942</v>
+        <v>588992</v>
       </c>
       <c r="R331" t="n">
-        <v>7042783</v>
+        <v>7042690</v>
       </c>
       <c r="S331" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -35185,12 +35200,12 @@
       </c>
       <c r="Y331" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -35205,27 +35220,27 @@
       <c r="AT331" t="inlineStr"/>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
       <c r="AZ331" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135841732</t>
+          <t>https://artportalen.se/Sighting/135860341</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>135844359</v>
+        <v>135864246</v>
       </c>
       <c r="B332" t="n">
-        <v>80538</v>
+        <v>99148</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -35233,21 +35248,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>229497</v>
+        <v>223049</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
@@ -35257,13 +35272,13 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>588613</v>
+        <v>588725</v>
       </c>
       <c r="R332" t="n">
-        <v>7042670</v>
+        <v>7042729</v>
       </c>
       <c r="S332" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -35287,12 +35302,12 @@
       </c>
       <c r="Y332" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -35307,27 +35322,27 @@
       <c r="AT332" t="inlineStr"/>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
       <c r="AZ332" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135844359</t>
+          <t>https://artportalen.se/Sighting/135864246</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>135845853</v>
+        <v>135864056</v>
       </c>
       <c r="B333" t="n">
-        <v>80538</v>
+        <v>98393</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -35335,21 +35350,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>229497</v>
+        <v>223358</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
@@ -35359,13 +35374,13 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>588870</v>
+        <v>588708</v>
       </c>
       <c r="R333" t="n">
-        <v>7042799</v>
+        <v>7042743</v>
       </c>
       <c r="S333" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -35389,12 +35404,12 @@
       </c>
       <c r="Y333" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -35409,24 +35424,24 @@
       <c r="AT333" t="inlineStr"/>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
       <c r="AZ333" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135845853</t>
+          <t>https://artportalen.se/Sighting/135864056</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>135846119</v>
+        <v>135841306</v>
       </c>
       <c r="B334" t="n">
         <v>80538</v>
@@ -35461,10 +35476,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>588967</v>
+        <v>588936</v>
       </c>
       <c r="R334" t="n">
-        <v>7042822</v>
+        <v>7042791</v>
       </c>
       <c r="S334" t="n">
         <v>15</v>
@@ -35522,16 +35537,16 @@
       <c r="AY334" t="inlineStr"/>
       <c r="AZ334" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135846119</t>
+          <t>https://artportalen.se/Sighting/135841306</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>135864257</v>
+        <v>135841732</v>
       </c>
       <c r="B335" t="n">
-        <v>80539</v>
+        <v>80538</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -35563,10 +35578,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>588715</v>
+        <v>588942</v>
       </c>
       <c r="R335" t="n">
-        <v>7042731</v>
+        <v>7042783</v>
       </c>
       <c r="S335" t="n">
         <v>15</v>
@@ -35593,12 +35608,12 @@
       </c>
       <c r="Y335" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -35624,16 +35639,16 @@
       <c r="AY335" t="inlineStr"/>
       <c r="AZ335" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864257</t>
+          <t>https://artportalen.se/Sighting/135841732</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>135864860</v>
+        <v>135844359</v>
       </c>
       <c r="B336" t="n">
-        <v>80539</v>
+        <v>80538</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -35665,13 +35680,13 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>588691</v>
+        <v>588613</v>
       </c>
       <c r="R336" t="n">
-        <v>7042728</v>
+        <v>7042670</v>
       </c>
       <c r="S336" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -35695,12 +35710,12 @@
       </c>
       <c r="Y336" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -35715,27 +35730,27 @@
       <c r="AT336" t="inlineStr"/>
       <c r="AW336" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
       <c r="AZ336" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864860</t>
+          <t>https://artportalen.se/Sighting/135844359</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>135865910</v>
+        <v>135845853</v>
       </c>
       <c r="B337" t="n">
-        <v>80539</v>
+        <v>80538</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -35767,13 +35782,13 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>588631</v>
+        <v>588870</v>
       </c>
       <c r="R337" t="n">
-        <v>7042744</v>
+        <v>7042799</v>
       </c>
       <c r="S337" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -35797,22 +35812,12 @@
       </c>
       <c r="Y337" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="Z337" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB337" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -35827,27 +35832,27 @@
       <c r="AT337" t="inlineStr"/>
       <c r="AW337" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
       <c r="AZ337" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135865910</t>
+          <t>https://artportalen.se/Sighting/135845853</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>136858115</v>
+        <v>135846119</v>
       </c>
       <c r="B338" t="n">
-        <v>80547</v>
+        <v>80538</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -35875,17 +35880,17 @@
       <c r="I338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Lövbränna vid Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>588943</v>
+        <v>588967</v>
       </c>
       <c r="R338" t="n">
-        <v>7042773</v>
+        <v>7042822</v>
       </c>
       <c r="S338" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -35909,12 +35914,12 @@
       </c>
       <c r="Y338" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -35929,69 +35934,62 @@
       <c r="AT338" t="inlineStr"/>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>Kristin Lindström, Anna-Maria Eriksson, Pernilla Hansson</t>
-        </is>
-      </c>
-      <c r="AY338" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY338" t="inlineStr"/>
       <c r="AZ338" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136858115</t>
+          <t>https://artportalen.se/Sighting/135846119</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>135838722</v>
+        <v>135864257</v>
       </c>
       <c r="B339" t="n">
-        <v>75488</v>
+        <v>80539</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>229651</v>
+        <v>229497</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
-      <c r="N339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>589132</v>
+        <v>588715</v>
       </c>
       <c r="R339" t="n">
-        <v>7042858</v>
+        <v>7042731</v>
       </c>
       <c r="S339" t="n">
         <v>15</v>
@@ -36018,12 +36016,12 @@
       </c>
       <c r="Y339" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -36032,7 +36030,6 @@
       <c r="AE339" t="b">
         <v>0</v>
       </c>
-      <c r="AF339" t="inlineStr"/>
       <c r="AG339" t="b">
         <v>0</v>
       </c>
@@ -36050,57 +36047,54 @@
       <c r="AY339" t="inlineStr"/>
       <c r="AZ339" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135838722</t>
+          <t>https://artportalen.se/Sighting/135864257</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>135839052</v>
+        <v>135864860</v>
       </c>
       <c r="B340" t="n">
-        <v>75488</v>
+        <v>80539</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>229651</v>
+        <v>229497</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>589066</v>
+        <v>588691</v>
       </c>
       <c r="R340" t="n">
-        <v>7042832</v>
+        <v>7042728</v>
       </c>
       <c r="S340" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -36124,12 +36118,12 @@
       </c>
       <c r="Y340" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -36138,75 +36132,71 @@
       <c r="AE340" t="b">
         <v>0</v>
       </c>
-      <c r="AF340" t="inlineStr"/>
       <c r="AG340" t="b">
         <v>0</v>
       </c>
       <c r="AT340" t="inlineStr"/>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
       <c r="AZ340" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135839052</t>
+          <t>https://artportalen.se/Sighting/135864860</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>135839215</v>
+        <v>135865910</v>
       </c>
       <c r="B341" t="n">
-        <v>75488</v>
+        <v>80539</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>229651</v>
+        <v>229497</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr"/>
-      <c r="N341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>589089</v>
+        <v>588631</v>
       </c>
       <c r="R341" t="n">
-        <v>7042794</v>
+        <v>7042744</v>
       </c>
       <c r="S341" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -36230,12 +36220,22 @@
       </c>
       <c r="Y341" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -36244,72 +36244,71 @@
       <c r="AE341" t="b">
         <v>0</v>
       </c>
-      <c r="AF341" t="inlineStr"/>
       <c r="AG341" t="b">
         <v>0</v>
       </c>
       <c r="AT341" t="inlineStr"/>
       <c r="AW341" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
       <c r="AZ341" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135839215</t>
+          <t>https://artportalen.se/Sighting/135865910</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>135863127</v>
+        <v>136858115</v>
       </c>
       <c r="B342" t="n">
-        <v>75488</v>
+        <v>80547</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>229651</v>
+        <v>229497</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Lövbränna vid Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>588894</v>
+        <v>588943</v>
       </c>
       <c r="R342" t="n">
-        <v>7042731</v>
+        <v>7042773</v>
       </c>
       <c r="S342" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -36333,12 +36332,12 @@
       </c>
       <c r="Y342" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD342" t="b">
@@ -36353,24 +36352,28 @@
       <c r="AT342" t="inlineStr"/>
       <c r="AW342" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kristin Lindström</t>
         </is>
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY342" t="inlineStr"/>
+          <t>Kristin Lindström, Anna-Maria Eriksson, Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AY342" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
       <c r="AZ342" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135863127</t>
+          <t>https://artportalen.se/Sighting/136858115</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>135864126</v>
+        <v>135838722</v>
       </c>
       <c r="B343" t="n">
         <v>75488</v>
@@ -36399,16 +36402,19 @@
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr"/>
+      <c r="K343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>588761</v>
+        <v>589132</v>
       </c>
       <c r="R343" t="n">
-        <v>7042749</v>
+        <v>7042858</v>
       </c>
       <c r="S343" t="n">
         <v>15</v>
@@ -36435,12 +36441,12 @@
       </c>
       <c r="Y343" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -36449,6 +36455,7 @@
       <c r="AE343" t="b">
         <v>0</v>
       </c>
+      <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="b">
         <v>0</v>
       </c>
@@ -36466,13 +36473,13 @@
       <c r="AY343" t="inlineStr"/>
       <c r="AZ343" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864126</t>
+          <t>https://artportalen.se/Sighting/135838722</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>135866016</v>
+        <v>135839052</v>
       </c>
       <c r="B344" t="n">
         <v>75488</v>
@@ -36501,19 +36508,22 @@
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
       <c r="P344" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>588613</v>
+        <v>589066</v>
       </c>
       <c r="R344" t="n">
-        <v>7042735</v>
+        <v>7042832</v>
       </c>
       <c r="S344" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T344" t="inlineStr">
         <is>
@@ -36537,22 +36547,12 @@
       </c>
       <c r="Y344" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="Z344" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB344" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD344" t="b">
@@ -36561,30 +36561,31 @@
       <c r="AE344" t="b">
         <v>0</v>
       </c>
+      <c r="AF344" t="inlineStr"/>
       <c r="AG344" t="b">
         <v>0</v>
       </c>
       <c r="AT344" t="inlineStr"/>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
       <c r="AZ344" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135866016</t>
+          <t>https://artportalen.se/Sighting/135839052</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>135866023</v>
+        <v>135839215</v>
       </c>
       <c r="B345" t="n">
         <v>75488</v>
@@ -36613,19 +36614,22 @@
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
+      <c r="J345" t="inlineStr"/>
+      <c r="K345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>588617</v>
+        <v>589089</v>
       </c>
       <c r="R345" t="n">
-        <v>7042729</v>
+        <v>7042794</v>
       </c>
       <c r="S345" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -36649,12 +36653,12 @@
       </c>
       <c r="Y345" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD345" t="b">
@@ -36663,30 +36667,31 @@
       <c r="AE345" t="b">
         <v>0</v>
       </c>
+      <c r="AF345" t="inlineStr"/>
       <c r="AG345" t="b">
         <v>0</v>
       </c>
       <c r="AT345" t="inlineStr"/>
       <c r="AW345" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
       <c r="AZ345" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135866023</t>
+          <t>https://artportalen.se/Sighting/135839215</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>135866114</v>
+        <v>135863127</v>
       </c>
       <c r="B346" t="n">
         <v>75488</v>
@@ -36721,10 +36726,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>588620</v>
+        <v>588894</v>
       </c>
       <c r="R346" t="n">
-        <v>7042684</v>
+        <v>7042731</v>
       </c>
       <c r="S346" t="n">
         <v>15</v>
@@ -36782,13 +36787,13 @@
       <c r="AY346" t="inlineStr"/>
       <c r="AZ346" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135866114</t>
+          <t>https://artportalen.se/Sighting/135863127</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>135867119</v>
+        <v>135864126</v>
       </c>
       <c r="B347" t="n">
         <v>75488</v>
@@ -36823,13 +36828,13 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>588553</v>
+        <v>588761</v>
       </c>
       <c r="R347" t="n">
-        <v>7042670</v>
+        <v>7042749</v>
       </c>
       <c r="S347" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -36856,19 +36861,9 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="Z347" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA347" t="inlineStr">
         <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB347" t="inlineStr">
-        <is>
-          <t>16:54</t>
         </is>
       </c>
       <c r="AD347" t="b">
@@ -36883,24 +36878,24 @@
       <c r="AT347" t="inlineStr"/>
       <c r="AW347" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
       <c r="AZ347" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135867119</t>
+          <t>https://artportalen.se/Sighting/135864126</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>135879813</v>
+        <v>135866016</v>
       </c>
       <c r="B348" t="n">
         <v>75488</v>
@@ -36931,17 +36926,17 @@
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>589121</v>
+        <v>588613</v>
       </c>
       <c r="R348" t="n">
-        <v>7042858</v>
+        <v>7042735</v>
       </c>
       <c r="S348" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -36968,14 +36963,19 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA348" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AC348" t="inlineStr">
-        <is>
-          <t>Ytterligare en lavparasit (grönfärgad) växte på samma plats</t>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD348" t="b">
@@ -36990,49 +36990,49 @@
       <c r="AT348" t="inlineStr"/>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
       <c r="AZ348" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135879813</t>
+          <t>https://artportalen.se/Sighting/135866016</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>135862479</v>
+        <v>135866023</v>
       </c>
       <c r="B349" t="n">
-        <v>80064</v>
+        <v>75488</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>229821</v>
+        <v>229651</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I349" t="inlineStr"/>
@@ -37042,10 +37042,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>588859</v>
+        <v>588617</v>
       </c>
       <c r="R349" t="n">
-        <v>7042626</v>
+        <v>7042729</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -37103,16 +37103,16 @@
       <c r="AY349" t="inlineStr"/>
       <c r="AZ349" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135862479</t>
+          <t>https://artportalen.se/Sighting/135866023</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>135886946</v>
+        <v>135866114</v>
       </c>
       <c r="B350" t="n">
-        <v>77102</v>
+        <v>75488</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -37120,35 +37120,37 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>266100</v>
+        <v>229651</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Lunglavsknapp</t>
+        </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Abrothallus diederichii</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Suija &amp; F.Berger</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I350" t="inlineStr"/>
-      <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
-      <c r="N350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>589121</v>
+        <v>588620</v>
       </c>
       <c r="R350" t="n">
-        <v>7042858</v>
+        <v>7042684</v>
       </c>
       <c r="S350" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -37180,45 +37182,39 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AC350" t="inlineStr">
-        <is>
-          <t>På lunglav, även lunglavsknapp på samma träd.</t>
-        </is>
-      </c>
       <c r="AD350" t="b">
         <v>0</v>
       </c>
       <c r="AE350" t="b">
         <v>0</v>
       </c>
-      <c r="AF350" t="inlineStr"/>
       <c r="AG350" t="b">
         <v>0</v>
       </c>
       <c r="AT350" t="inlineStr"/>
       <c r="AW350" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX350" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman, Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
       <c r="AZ350" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135886946</t>
+          <t>https://artportalen.se/Sighting/135866114</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>135839356</v>
+        <v>135867119</v>
       </c>
       <c r="B351" t="n">
-        <v>92447</v>
+        <v>75488</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -37226,35 +37222,37 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>6331024</v>
+        <v>229651</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Lunglavsknapp</t>
+        </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Skeletocutis delicata</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Miettinen &amp; Niemelä</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
-      <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr"/>
-      <c r="N351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
         <is>
           <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>589088</v>
+        <v>588553</v>
       </c>
       <c r="R351" t="n">
-        <v>7042814</v>
+        <v>7042670</v>
       </c>
       <c r="S351" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -37278,12 +37276,22 @@
       </c>
       <c r="Y351" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD351" t="b">
@@ -37292,34 +37300,33 @@
       <c r="AE351" t="b">
         <v>0</v>
       </c>
-      <c r="AF351" t="inlineStr"/>
       <c r="AG351" t="b">
         <v>0</v>
       </c>
       <c r="AT351" t="inlineStr"/>
       <c r="AW351" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
       <c r="AZ351" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135839356</t>
+          <t>https://artportalen.se/Sighting/135867119</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>135842385</v>
+        <v>135879813</v>
       </c>
       <c r="B352" t="n">
-        <v>92447</v>
+        <v>75488</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -37327,35 +37334,37 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>6331024</v>
+        <v>229651</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Lunglavsknapp</t>
+        </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Skeletocutis delicata</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Miettinen &amp; Niemelä</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
-      <c r="N352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+          <t>Nyfäbodberget, Ång</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>588845</v>
+        <v>589121</v>
       </c>
       <c r="R352" t="n">
-        <v>7042752</v>
+        <v>7042858</v>
       </c>
       <c r="S352" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -37379,12 +37388,17 @@
       </c>
       <c r="Y352" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>Ytterligare en lavparasit (grönfärgad) växte på samma plats</t>
         </is>
       </c>
       <c r="AD352" t="b">
@@ -37393,23 +37407,432 @@
       <c r="AE352" t="b">
         <v>0</v>
       </c>
-      <c r="AF352" t="inlineStr"/>
       <c r="AG352" t="b">
         <v>0</v>
       </c>
       <c r="AT352" t="inlineStr"/>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
       <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135879813</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>135862479</v>
+      </c>
+      <c r="B353" t="n">
+        <v>80064</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr"/>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q353" t="n">
+        <v>588859</v>
+      </c>
+      <c r="R353" t="n">
+        <v>7042626</v>
+      </c>
+      <c r="S353" t="n">
+        <v>10</v>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AD353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG353" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT353" t="inlineStr"/>
+      <c r="AW353" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX353" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135862479</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>135886946</v>
+      </c>
+      <c r="B354" t="n">
+        <v>77102</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>266100</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Abrothallus diederichii</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Suija &amp; F.Berger</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>Nyfäbodberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q354" t="n">
+        <v>589121</v>
+      </c>
+      <c r="R354" t="n">
+        <v>7042858</v>
+      </c>
+      <c r="S354" t="n">
+        <v>25</v>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AC354" t="inlineStr">
+        <is>
+          <t>På lunglav, även lunglavsknapp på samma träd.</t>
+        </is>
+      </c>
+      <c r="AD354" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE354" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF354" t="inlineStr"/>
+      <c r="AG354" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT354" t="inlineStr"/>
+      <c r="AW354" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX354" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Daniel Rutschman, Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135886946</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>135839356</v>
+      </c>
+      <c r="B355" t="n">
+        <v>92447</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>6331024</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Skeletocutis delicata</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Miettinen &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q355" t="n">
+        <v>589088</v>
+      </c>
+      <c r="R355" t="n">
+        <v>7042814</v>
+      </c>
+      <c r="S355" t="n">
+        <v>15</v>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD355" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE355" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF355" t="inlineStr"/>
+      <c r="AG355" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT355" t="inlineStr"/>
+      <c r="AW355" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX355" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135839356</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>135842385</v>
+      </c>
+      <c r="B356" t="n">
+        <v>92447</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>6331024</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Skeletocutis delicata</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Miettinen &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>Nyfäbodberget, Nyfäbodberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q356" t="n">
+        <v>588845</v>
+      </c>
+      <c r="R356" t="n">
+        <v>7042752</v>
+      </c>
+      <c r="S356" t="n">
+        <v>15</v>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD356" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE356" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF356" t="inlineStr"/>
+      <c r="AG356" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT356" t="inlineStr"/>
+      <c r="AW356" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX356" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135842385</t>
         </is>
@@ -37768,6 +38191,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -5093,7 +5093,7 @@
         <v>136858131</v>
       </c>
       <c r="B45" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>137032964</v>
       </c>
       <c r="B46" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>137033782</v>
       </c>
       <c r="B47" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>137033761</v>
       </c>
       <c r="B50" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>136858117</v>
       </c>
       <c r="B79" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>137033011</v>
       </c>
       <c r="B80" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>137033666</v>
       </c>
       <c r="B81" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>137033696</v>
       </c>
       <c r="B82" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>137033823</v>
       </c>
       <c r="B83" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>136858105</v>
       </c>
       <c r="B89" t="n">
-        <v>92128</v>
+        <v>92129</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>136858126</v>
       </c>
       <c r="B94" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>136858130</v>
       </c>
       <c r="B95" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>136858134</v>
       </c>
       <c r="B99" t="n">
-        <v>92950</v>
+        <v>92951</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>137033816</v>
       </c>
       <c r="B120" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>136858113</v>
       </c>
       <c r="B243" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>137033711</v>
       </c>
       <c r="B244" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>137077842</v>
       </c>
       <c r="B245" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>137078302</v>
       </c>
       <c r="B246" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>137078308</v>
       </c>
       <c r="B298" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>137078295</v>
       </c>
       <c r="B329" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>136858115</v>
       </c>
       <c r="B342" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -5093,7 +5093,7 @@
         <v>136858131</v>
       </c>
       <c r="B45" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>137032964</v>
       </c>
       <c r="B46" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>137033782</v>
       </c>
       <c r="B47" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>137033761</v>
       </c>
       <c r="B50" t="n">
-        <v>92834</v>
+        <v>92840</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>136858117</v>
       </c>
       <c r="B79" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>137033011</v>
       </c>
       <c r="B80" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>137033666</v>
       </c>
       <c r="B81" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>137033696</v>
       </c>
       <c r="B82" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>137033823</v>
       </c>
       <c r="B83" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>136858105</v>
       </c>
       <c r="B89" t="n">
-        <v>92129</v>
+        <v>92135</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>137118109</v>
       </c>
       <c r="B90" t="n">
-        <v>92129</v>
+        <v>92135</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>136858126</v>
       </c>
       <c r="B95" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>136858130</v>
       </c>
       <c r="B96" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>136858134</v>
       </c>
       <c r="B100" t="n">
-        <v>92951</v>
+        <v>92957</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>137033816</v>
       </c>
       <c r="B121" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>137078308</v>
       </c>
       <c r="B301" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>137078295</v>
       </c>
       <c r="B332" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
